--- a/Distribucion/Excels/subestaciones_distribucion.xlsx
+++ b/Distribucion/Excels/subestaciones_distribucion.xlsx
@@ -40717,7 +40717,7 @@
         <v>42.62643782236754</v>
       </c>
       <c r="F1221" t="n">
-        <v>-1.713381094336294</v>
+        <v>-7.713381094336302</v>
       </c>
       <c r="G1221" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>42.6254581272887</v>
       </c>
       <c r="F1222" t="n">
-        <v>-1.768447803816246</v>
+        <v>-7.768447803816255</v>
       </c>
       <c r="G1222" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>42.92547519239591</v>
       </c>
       <c r="F1223" t="n">
-        <v>-1.359797716940234</v>
+        <v>-7.359797716940244</v>
       </c>
       <c r="G1223" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>43.12370188347003</v>
       </c>
       <c r="F1224" t="n">
-        <v>-1.644123379212722</v>
+        <v>-7.644123379212731</v>
       </c>
       <c r="G1224" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>43.02017378502241</v>
       </c>
       <c r="F1225" t="n">
-        <v>-1.8170406629779</v>
+        <v>-7.817040662977908</v>
       </c>
       <c r="G1225" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>43.01842584088055</v>
       </c>
       <c r="F1226" t="n">
-        <v>-1.573681207817912</v>
+        <v>-7.57368120781792</v>
       </c>
       <c r="G1226" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>42.51128702634079</v>
       </c>
       <c r="F1227" t="n">
-        <v>-1.513478093681456</v>
+        <v>-7.513478093681464</v>
       </c>
       <c r="G1227" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>42.79724179482108</v>
       </c>
       <c r="F1228" t="n">
-        <v>-1.247254582479423</v>
+        <v>-7.247254582479431</v>
       </c>
       <c r="G1228" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>42.86631143036445</v>
       </c>
       <c r="F1229" t="n">
-        <v>-1.868485986668582</v>
+        <v>-7.86848598666859</v>
       </c>
       <c r="G1229" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>42.46767617154996</v>
       </c>
       <c r="F1230" t="n">
-        <v>-1.726928488720461</v>
+        <v>-7.726928488720469</v>
       </c>
       <c r="G1230" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>42.77632059449685</v>
       </c>
       <c r="F1231" t="n">
-        <v>-1.423614127886524</v>
+        <v>-7.423614127886533</v>
       </c>
       <c r="G1231" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>42.75889770989652</v>
       </c>
       <c r="F1232" t="n">
-        <v>-1.227927718559496</v>
+        <v>-7.227927718559505</v>
       </c>
       <c r="G1232" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>42.13766185838121</v>
       </c>
       <c r="F1328" t="n">
-        <v>-2.621945790887332</v>
+        <v>-8.62194579088734</v>
       </c>
       <c r="G1328" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>42.21059008795999</v>
       </c>
       <c r="F1329" t="n">
-        <v>-2.735850054308774</v>
+        <v>-8.735850054308784</v>
       </c>
       <c r="G1329" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>42.51990031068164</v>
       </c>
       <c r="F1330" t="n">
-        <v>-2.674860434548688</v>
+        <v>-8.674860434548696</v>
       </c>
       <c r="G1330" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>42.23466911767782</v>
       </c>
       <c r="F1331" t="n">
-        <v>-2.72652684724356</v>
+        <v>-8.726526847243569</v>
       </c>
       <c r="G1331" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>42.51288896071031</v>
       </c>
       <c r="F1332" t="n">
-        <v>-2.783309096530071</v>
+        <v>-8.783309096530079</v>
       </c>
       <c r="G1332" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>42.2896579994608</v>
       </c>
       <c r="F1333" t="n">
-        <v>-2.784100122192769</v>
+        <v>-8.784100122192777</v>
       </c>
       <c r="G1333" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>42.1129466219379</v>
       </c>
       <c r="F1334" t="n">
-        <v>-2.81080432347615</v>
+        <v>-8.810804323476161</v>
       </c>
       <c r="G1334" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>42.65223638218523</v>
       </c>
       <c r="F1335" t="n">
-        <v>-2.111530468805121</v>
+        <v>-8.11153046880513</v>
       </c>
       <c r="G1335" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>42.68498340074346</v>
       </c>
       <c r="F1336" t="n">
-        <v>-2.503891372729513</v>
+        <v>-8.503891372729523</v>
       </c>
       <c r="G1336" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>42.41731190342755</v>
       </c>
       <c r="F1337" t="n">
-        <v>-2.664780099388735</v>
+        <v>-8.664780099388743</v>
       </c>
       <c r="G1337" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>42.21537782284174</v>
       </c>
       <c r="F1338" t="n">
-        <v>-2.644478112648293</v>
+        <v>-8.644478112648301</v>
       </c>
       <c r="G1338" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>42.43818451747543</v>
       </c>
       <c r="F1339" t="n">
-        <v>-2.620412024518123</v>
+        <v>-8.620412024518131</v>
       </c>
       <c r="G1339" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>42.76940468935944</v>
       </c>
       <c r="F1340" t="n">
-        <v>-2.349892571508382</v>
+        <v>-8.34989257150839</v>
       </c>
       <c r="G1340" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>42.85366369255738</v>
       </c>
       <c r="F1341" t="n">
-        <v>-2.189711093422901</v>
+        <v>-8.189711093422909</v>
       </c>
       <c r="G1341" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>42.35001807595149</v>
       </c>
       <c r="F1342" t="n">
-        <v>-2.613099575852009</v>
+        <v>-8.613099575852017</v>
       </c>
       <c r="G1342" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>42.18487973673584</v>
       </c>
       <c r="F1343" t="n">
-        <v>-2.50524092683424</v>
+        <v>-8.505240926834247</v>
       </c>
       <c r="G1343" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>42.3665837727883</v>
       </c>
       <c r="F1344" t="n">
-        <v>-2.554521455418412</v>
+        <v>-8.554521455418421</v>
       </c>
       <c r="G1344" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>42.26318187074592</v>
       </c>
       <c r="F1345" t="n">
-        <v>-2.590120984932759</v>
+        <v>-8.590120984932767</v>
       </c>
       <c r="G1345" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>42.28481954430262</v>
       </c>
       <c r="F1346" t="n">
-        <v>-2.62300784589095</v>
+        <v>-8.623007845890958</v>
       </c>
       <c r="G1346" t="inlineStr">
         <is>
@@ -44875,7 +44875,7 @@
         <v>41.92784372679003</v>
       </c>
       <c r="F1347" t="n">
-        <v>-2.84811447665147</v>
+        <v>-8.848114476651478</v>
       </c>
       <c r="G1347" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>42.08962903924376</v>
       </c>
       <c r="F1348" t="n">
-        <v>-2.465341744840273</v>
+        <v>-8.465341744840281</v>
       </c>
       <c r="G1348" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>42.43643077989049</v>
       </c>
       <c r="F1349" t="n">
-        <v>-2.80447256239554</v>
+        <v>-8.804472562395548</v>
       </c>
       <c r="G1349" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>42.21106749249508</v>
       </c>
       <c r="F1350" t="n">
-        <v>-2.699297629210959</v>
+        <v>-8.699297629210967</v>
       </c>
       <c r="G1350" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>42.52306545926947</v>
       </c>
       <c r="F1351" t="n">
-        <v>-2.521854058985565</v>
+        <v>-8.521854058985573</v>
       </c>
       <c r="G1351" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>42.5855503604643</v>
       </c>
       <c r="F1352" t="n">
-        <v>-2.643856813609201</v>
+        <v>-8.64385681360921</v>
       </c>
       <c r="G1352" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>42.24434275778702</v>
       </c>
       <c r="F1353" t="n">
-        <v>-2.694751794129544</v>
+        <v>-8.694751794129552</v>
       </c>
       <c r="G1353" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>42.05539538509405</v>
       </c>
       <c r="F1354" t="n">
-        <v>-2.658955519901601</v>
+        <v>-8.65895551990161</v>
       </c>
       <c r="G1354" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>42.17507601467891</v>
       </c>
       <c r="F1355" t="n">
-        <v>-2.708960823268928</v>
+        <v>-8.708960823268937</v>
       </c>
       <c r="G1355" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>42.59588509324396</v>
       </c>
       <c r="F1356" t="n">
-        <v>-2.747527130822156</v>
+        <v>-8.747527130822164</v>
       </c>
       <c r="G1356" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>42.44296033466445</v>
       </c>
       <c r="F1357" t="n">
-        <v>-2.833099838253204</v>
+        <v>-8.833099838253212</v>
       </c>
       <c r="G1357" t="inlineStr">
         <is>

--- a/Distribucion/Excels/subestaciones_distribucion.xlsx
+++ b/Distribucion/Excels/subestaciones_distribucion.xlsx
@@ -38077,7 +38077,7 @@
         <v>43.47500810572026</v>
       </c>
       <c r="F1141" t="n">
-        <v>-2.174211171467115</v>
+        <v>-8.174211171467123</v>
       </c>
       <c r="G1141" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>43.27984396768383</v>
       </c>
       <c r="F1142" t="n">
-        <v>-2.240192144041855</v>
+        <v>-8.240192144041863</v>
       </c>
       <c r="G1142" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>43.09694375977974</v>
       </c>
       <c r="F1143" t="n">
-        <v>-2.774502628858523</v>
+        <v>-8.774502628858531</v>
       </c>
       <c r="G1143" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>42.66969401566848</v>
       </c>
       <c r="F1144" t="n">
-        <v>-2.871045447463434</v>
+        <v>-8.871045447463443</v>
       </c>
       <c r="G1144" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>43.23245265940853</v>
       </c>
       <c r="F1145" t="n">
-        <v>-2.68160272353976</v>
+        <v>-8.681602723539768</v>
       </c>
       <c r="G1145" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>43.2152617988873</v>
       </c>
       <c r="F1146" t="n">
-        <v>-2.886104025481511</v>
+        <v>-8.886104025481519</v>
       </c>
       <c r="G1146" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>43.20508788880588</v>
       </c>
       <c r="F1147" t="n">
-        <v>-2.68508100479393</v>
+        <v>-8.68508100479394</v>
       </c>
       <c r="G1147" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>43.63811475406554</v>
       </c>
       <c r="F1148" t="n">
-        <v>-2.037875006717189</v>
+        <v>-8.037875006717197</v>
       </c>
       <c r="G1148" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>43.13639179065881</v>
       </c>
       <c r="F1149" t="n">
-        <v>-2.155678559161327</v>
+        <v>-8.155678559161336</v>
       </c>
       <c r="G1149" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>43.02645068447703</v>
       </c>
       <c r="F1150" t="n">
-        <v>-2.792472124349327</v>
+        <v>-8.792472124349336</v>
       </c>
       <c r="G1150" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>43.50902804182268</v>
       </c>
       <c r="F1151" t="n">
-        <v>-2.169491784807053</v>
+        <v>-8.169491784807061</v>
       </c>
       <c r="G1151" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>43.16584869872062</v>
       </c>
       <c r="F1152" t="n">
-        <v>-2.925131125855081</v>
+        <v>-8.92513112585509</v>
       </c>
       <c r="G1152" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>43.15588163178695</v>
       </c>
       <c r="F1153" t="n">
-        <v>-3.173316750723833</v>
+        <v>-9.173316750723842</v>
       </c>
       <c r="G1153" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>43.3429952237728</v>
       </c>
       <c r="F1154" t="n">
-        <v>-2.397867553555295</v>
+        <v>-8.397867553555303</v>
       </c>
       <c r="G1154" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>43.3667085330877</v>
       </c>
       <c r="F1155" t="n">
-        <v>-2.402150321917203</v>
+        <v>-8.402150321917212</v>
       </c>
       <c r="G1155" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>43.40572455733638</v>
       </c>
       <c r="F1156" t="n">
-        <v>-2.044216515493278</v>
+        <v>-8.044216515493288</v>
       </c>
       <c r="G1156" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>42.91448981657607</v>
       </c>
       <c r="F1157" t="n">
-        <v>-2.494580881167854</v>
+        <v>-8.494580881167861</v>
       </c>
       <c r="G1157" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>43.47448498763491</v>
       </c>
       <c r="F1158" t="n">
-        <v>-2.039251087391115</v>
+        <v>-8.039251087391124</v>
       </c>
       <c r="G1158" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>43.34267837884101</v>
       </c>
       <c r="F1159" t="n">
-        <v>-2.42914606085572</v>
+        <v>-8.429146060855729</v>
       </c>
       <c r="G1159" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>43.25069886284857</v>
       </c>
       <c r="F1160" t="n">
-        <v>-2.579298052207804</v>
+        <v>-8.579298052207813</v>
       </c>
       <c r="G1160" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>43.66476411329241</v>
       </c>
       <c r="F1161" t="n">
-        <v>-1.891476985680837</v>
+        <v>-7.891476985680846</v>
       </c>
       <c r="G1161" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>43.51332082760207</v>
       </c>
       <c r="F1162" t="n">
-        <v>-2.163011794701776</v>
+        <v>-8.163011794701783</v>
       </c>
       <c r="G1162" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>43.16913122769822</v>
       </c>
       <c r="F1163" t="n">
-        <v>-2.409555530265396</v>
+        <v>-8.409555530265404</v>
       </c>
       <c r="G1163" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>42.91203337016726</v>
       </c>
       <c r="F1164" t="n">
-        <v>-2.034987142553175</v>
+        <v>-8.034987142553183</v>
       </c>
       <c r="G1164" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>43.16806728416135</v>
       </c>
       <c r="F1165" t="n">
-        <v>-2.355891201124099</v>
+        <v>-8.355891201124107</v>
       </c>
       <c r="G1165" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>43.43377350401617</v>
       </c>
       <c r="F1166" t="n">
-        <v>-1.854174842692247</v>
+        <v>-7.854174842692255</v>
       </c>
       <c r="G1166" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>43.29924499084158</v>
       </c>
       <c r="F1167" t="n">
-        <v>-2.487139675594317</v>
+        <v>-8.487139675594324</v>
       </c>
       <c r="G1167" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>42.78498620464142</v>
       </c>
       <c r="F1168" t="n">
-        <v>-3.074212650517391</v>
+        <v>-9.074212650517399</v>
       </c>
       <c r="G1168" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>43.05644186060967</v>
       </c>
       <c r="F1169" t="n">
-        <v>-3.233269457741351</v>
+        <v>-9.233269457741359</v>
       </c>
       <c r="G1169" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>42.89176475443433</v>
       </c>
       <c r="F1170" t="n">
-        <v>-3.029772958994332</v>
+        <v>-9.029772958994339</v>
       </c>
       <c r="G1170" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>42.91584098081738</v>
       </c>
       <c r="F1171" t="n">
-        <v>-2.73581077192851</v>
+        <v>-8.735810771928518</v>
       </c>
       <c r="G1171" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>42.74162276938289</v>
       </c>
       <c r="F1172" t="n">
-        <v>-2.657381628969842</v>
+        <v>-8.657381628969851</v>
       </c>
       <c r="G1172" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>42.72640173899076</v>
       </c>
       <c r="F1173" t="n">
-        <v>-2.985867677575239</v>
+        <v>-8.985867677575248</v>
       </c>
       <c r="G1173" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>43.32495874830874</v>
       </c>
       <c r="F1174" t="n">
-        <v>-2.211212977030921</v>
+        <v>-8.211212977030929</v>
       </c>
       <c r="G1174" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>43.46831076142712</v>
       </c>
       <c r="F1175" t="n">
-        <v>-2.320901966195391</v>
+        <v>-8.320901966195398</v>
       </c>
       <c r="G1175" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>43.43965795680131</v>
       </c>
       <c r="F1176" t="n">
-        <v>-1.860044584584739</v>
+        <v>-7.860044584584748</v>
       </c>
       <c r="G1176" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>42.57583356681521</v>
       </c>
       <c r="F1177" t="n">
-        <v>-2.970779891400893</v>
+        <v>-8.970779891400902</v>
       </c>
       <c r="G1177" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>42.94717734094524</v>
       </c>
       <c r="F1178" t="n">
-        <v>-3.170155862037196</v>
+        <v>-9.170155862037205</v>
       </c>
       <c r="G1178" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>43.22533276302141</v>
       </c>
       <c r="F1179" t="n">
-        <v>-2.363095484119638</v>
+        <v>-8.363095484119645</v>
       </c>
       <c r="G1179" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>43.54066208582352</v>
       </c>
       <c r="F1180" t="n">
-        <v>-2.207874117552794</v>
+        <v>-8.207874117552803</v>
       </c>
       <c r="G1180" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>42.78760107797914</v>
       </c>
       <c r="F1181" t="n">
-        <v>-2.737909566831735</v>
+        <v>-8.737909566831743</v>
       </c>
       <c r="G1181" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>43.3508622357155</v>
       </c>
       <c r="F1182" t="n">
-        <v>-2.308208095349812</v>
+        <v>-8.308208095349821</v>
       </c>
       <c r="G1182" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>43.32840797233777</v>
       </c>
       <c r="F1183" t="n">
-        <v>-2.500746070610181</v>
+        <v>-8.500746070610189</v>
       </c>
       <c r="G1183" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>42.89154990928035</v>
       </c>
       <c r="F1184" t="n">
-        <v>-2.531852548056411</v>
+        <v>-8.53185254805642</v>
       </c>
       <c r="G1184" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>43.15137999933746</v>
       </c>
       <c r="F1185" t="n">
-        <v>-2.023788849789965</v>
+        <v>-8.023788849789973</v>
       </c>
       <c r="G1185" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>42.98150156229158</v>
       </c>
       <c r="F1186" t="n">
-        <v>-2.444996988511889</v>
+        <v>-8.444996988511898</v>
       </c>
       <c r="G1186" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>43.30956877881584</v>
       </c>
       <c r="F1187" t="n">
-        <v>-2.348295207878113</v>
+        <v>-8.348295207878122</v>
       </c>
       <c r="G1187" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>43.49438864972537</v>
       </c>
       <c r="F1188" t="n">
-        <v>-2.226178198668359</v>
+        <v>-8.226178198668368</v>
       </c>
       <c r="G1188" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>42.85479997194844</v>
       </c>
       <c r="F1189" t="n">
-        <v>-2.578347989771348</v>
+        <v>-8.578347989771357</v>
       </c>
       <c r="G1189" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>43.53834885451514</v>
       </c>
       <c r="F1190" t="n">
-        <v>-1.922733702777709</v>
+        <v>-7.922733702777719</v>
       </c>
       <c r="G1190" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>43.36966761030885</v>
       </c>
       <c r="F1191" t="n">
-        <v>-2.435138506387183</v>
+        <v>-8.43513850638719</v>
       </c>
       <c r="G1191" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>42.8325263722349</v>
       </c>
       <c r="F1192" t="n">
-        <v>-2.845379957598933</v>
+        <v>-8.845379957598942</v>
       </c>
       <c r="G1192" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>43.43965054963625</v>
       </c>
       <c r="F1193" t="n">
-        <v>-2.165856916196512</v>
+        <v>-8.165856916196521</v>
       </c>
       <c r="G1193" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>43.1011629158779</v>
       </c>
       <c r="F1194" t="n">
-        <v>-3.0483566689213</v>
+        <v>-9.048356668921308</v>
       </c>
       <c r="G1194" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>42.39795346412646</v>
       </c>
       <c r="F1308" t="n">
-        <v>-2.157289215320035</v>
+        <v>-8.157289215320043</v>
       </c>
       <c r="G1308" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>42.18278182147874</v>
       </c>
       <c r="F1309" t="n">
-        <v>-1.794417155665992</v>
+        <v>-7.794417155666</v>
       </c>
       <c r="G1309" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>42.33619342330225</v>
       </c>
       <c r="F1310" t="n">
-        <v>-1.867053601225507</v>
+        <v>-7.867053601225515</v>
       </c>
       <c r="G1310" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>42.4183605612434</v>
       </c>
       <c r="F1311" t="n">
-        <v>-1.005505072871706</v>
+        <v>-7.005505072871713</v>
       </c>
       <c r="G1311" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>42.2916510045028</v>
       </c>
       <c r="F1312" t="n">
-        <v>-2.113717122508475</v>
+        <v>-8.113717122508485</v>
       </c>
       <c r="G1312" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         <v>41.94101731784708</v>
       </c>
       <c r="F1313" t="n">
-        <v>-2.055292777148656</v>
+        <v>-8.055292777148665</v>
       </c>
       <c r="G1313" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>42.14602636633268</v>
       </c>
       <c r="F1314" t="n">
-        <v>-1.943185215918123</v>
+        <v>-7.943185215918132</v>
       </c>
       <c r="G1314" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>42.43603699374314</v>
       </c>
       <c r="F1315" t="n">
-        <v>-2.056415280275513</v>
+        <v>-8.056415280275521</v>
       </c>
       <c r="G1315" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>42.38874939169047</v>
       </c>
       <c r="F1316" t="n">
-        <v>-0.8625839321231518</v>
+        <v>-6.86258393212316</v>
       </c>
       <c r="G1316" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>42.15384748519664</v>
       </c>
       <c r="F1317" t="n">
-        <v>-2.193118804283134</v>
+        <v>-8.193118804283142</v>
       </c>
       <c r="G1317" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>41.95276958920449</v>
       </c>
       <c r="F1318" t="n">
-        <v>-1.64129534107808</v>
+        <v>-7.641295341078088</v>
       </c>
       <c r="G1318" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>42.38489163653953</v>
       </c>
       <c r="F1319" t="n">
-        <v>-1.509272741489286</v>
+        <v>-7.509272741489295</v>
       </c>
       <c r="G1319" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>42.39444092331676</v>
       </c>
       <c r="F1320" t="n">
-        <v>-1.125485076625873</v>
+        <v>-7.125485076625882</v>
       </c>
       <c r="G1320" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>42.35590492463772</v>
       </c>
       <c r="F1321" t="n">
-        <v>-1.950032962178306</v>
+        <v>-7.950032962178315</v>
       </c>
       <c r="G1321" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>42.2901190137455</v>
       </c>
       <c r="F1322" t="n">
-        <v>-1.818887721131923</v>
+        <v>-7.818887721131932</v>
       </c>
       <c r="G1322" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>41.95614484521879</v>
       </c>
       <c r="F1323" t="n">
-        <v>-1.981151524649366</v>
+        <v>-7.981151524649375</v>
       </c>
       <c r="G1323" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>42.12547419173919</v>
       </c>
       <c r="F1324" t="n">
-        <v>-1.678998547486863</v>
+        <v>-7.678998547486872</v>
       </c>
       <c r="G1324" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>41.93229190861292</v>
       </c>
       <c r="F1325" t="n">
-        <v>-1.465028707809272</v>
+        <v>-7.46502870780928</v>
       </c>
       <c r="G1325" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>42.3578598080344</v>
       </c>
       <c r="F1326" t="n">
-        <v>-1.84877813386191</v>
+        <v>-7.848778133861919</v>
       </c>
       <c r="G1326" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>42.0586444925318</v>
       </c>
       <c r="F1327" t="n">
-        <v>-1.706392761275467</v>
+        <v>-7.706392761275476</v>
       </c>
       <c r="G1327" t="inlineStr">
         <is>

--- a/Distribucion/Excels/subestaciones_distribucion.xlsx
+++ b/Distribucion/Excels/subestaciones_distribucion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2681"/>
+  <dimension ref="A1:G2739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88909,6 +88909,1819 @@
         </is>
       </c>
     </row>
+    <row r="2682">
+      <c r="A2682" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2682" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2682" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2682" t="inlineStr">
+        <is>
+          <t>BARREIROS</t>
+        </is>
+      </c>
+      <c r="E2682" t="n">
+        <v>43.47071136824527</v>
+      </c>
+      <c r="F2682" t="n">
+        <v>-7.258759612847358</v>
+      </c>
+      <c r="G2682" t="inlineStr">
+        <is>
+          <t>Boimente 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2683">
+      <c r="A2683" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2683" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2683" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2683" t="inlineStr">
+        <is>
+          <t>BEGONTE</t>
+        </is>
+      </c>
+      <c r="E2683" t="n">
+        <v>43.12284239061619</v>
+      </c>
+      <c r="F2683" t="n">
+        <v>-7.64669630070495</v>
+      </c>
+      <c r="G2683" t="inlineStr">
+        <is>
+          <t>P.G.R. 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2684" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2684" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2684" t="inlineStr">
+        <is>
+          <t>BURELA</t>
+        </is>
+      </c>
+      <c r="E2684" t="n">
+        <v>43.66531477425224</v>
+      </c>
+      <c r="F2684" t="n">
+        <v>-7.380930438285355</v>
+      </c>
+      <c r="G2684" t="inlineStr">
+        <is>
+          <t>Boimente 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2685" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2685" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2685" t="inlineStr">
+        <is>
+          <t>C_CONDE</t>
+        </is>
+      </c>
+      <c r="E2685" t="n">
+        <v>43.01515109124952</v>
+      </c>
+      <c r="F2685" t="n">
+        <v>-7.557017147558398</v>
+      </c>
+      <c r="G2685" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2686" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2686" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2686" t="inlineStr">
+        <is>
+          <t>CASTIÑEIRO</t>
+        </is>
+      </c>
+      <c r="E2686" t="n">
+        <v>43.01810333215821</v>
+      </c>
+      <c r="F2686" t="n">
+        <v>-7.565708555081163</v>
+      </c>
+      <c r="G2686" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2687">
+      <c r="A2687" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2687" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2687" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2687" t="inlineStr">
+        <is>
+          <t>CEAO</t>
+        </is>
+      </c>
+      <c r="E2687" t="n">
+        <v>43.04773114320447</v>
+      </c>
+      <c r="F2687" t="n">
+        <v>-7.560535620153551</v>
+      </c>
+      <c r="G2687" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2688">
+      <c r="A2688" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2688" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2688" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2688" t="inlineStr">
+        <is>
+          <t>FONSAGRADA</t>
+        </is>
+      </c>
+      <c r="E2688" t="n">
+        <v>43.08400658244803</v>
+      </c>
+      <c r="F2688" t="n">
+        <v>-7.132734734850848</v>
+      </c>
+      <c r="G2688" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2689" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2689" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2689" t="inlineStr">
+        <is>
+          <t>FOZ</t>
+        </is>
+      </c>
+      <c r="E2689" t="n">
+        <v>43.54942584345063</v>
+      </c>
+      <c r="F2689" t="n">
+        <v>-7.266366969765398</v>
+      </c>
+      <c r="G2689" t="inlineStr">
+        <is>
+          <t>Boimente 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2690" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2690" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2690" t="inlineStr">
+        <is>
+          <t>LUDRIO</t>
+        </is>
+      </c>
+      <c r="E2690" t="n">
+        <v>43.12849547542754</v>
+      </c>
+      <c r="F2690" t="n">
+        <v>-7.416742782538231</v>
+      </c>
+      <c r="G2690" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2691" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2691" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2691" t="inlineStr">
+        <is>
+          <t>MAGAZOS</t>
+        </is>
+      </c>
+      <c r="E2691" t="n">
+        <v>43.64619603760239</v>
+      </c>
+      <c r="F2691" t="n">
+        <v>-7.601878514675395</v>
+      </c>
+      <c r="G2691" t="inlineStr">
+        <is>
+          <t>Boimente 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2692" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2692" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2692" t="inlineStr">
+        <is>
+          <t>MEIRA</t>
+        </is>
+      </c>
+      <c r="E2692" t="n">
+        <v>43.22153807198773</v>
+      </c>
+      <c r="F2692" t="n">
+        <v>-7.318507385287498</v>
+      </c>
+      <c r="G2692" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2693" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2693" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2693" t="inlineStr">
+        <is>
+          <t>MERCEDES</t>
+        </is>
+      </c>
+      <c r="E2693" t="n">
+        <v>42.99789236676193</v>
+      </c>
+      <c r="F2693" t="n">
+        <v>-7.545984709456373</v>
+      </c>
+      <c r="G2693" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2694" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2694" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2694" t="inlineStr">
+        <is>
+          <t>MONDOÑEDO</t>
+        </is>
+      </c>
+      <c r="E2694" t="n">
+        <v>43.43183279816028</v>
+      </c>
+      <c r="F2694" t="n">
+        <v>-7.366828752764549</v>
+      </c>
+      <c r="G2694" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2695" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2695" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2695" t="inlineStr">
+        <is>
+          <t>RIBADEO</t>
+        </is>
+      </c>
+      <c r="E2695" t="n">
+        <v>43.53533808945408</v>
+      </c>
+      <c r="F2695" t="n">
+        <v>-7.073352974017291</v>
+      </c>
+      <c r="G2695" t="inlineStr">
+        <is>
+          <t>Salas 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2696" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2696" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2696" t="inlineStr">
+        <is>
+          <t>SAN_CIBRAO</t>
+        </is>
+      </c>
+      <c r="E2696" t="n">
+        <v>43.01701380534946</v>
+      </c>
+      <c r="F2696" t="n">
+        <v>-7.517322844503155</v>
+      </c>
+      <c r="G2696" t="inlineStr">
+        <is>
+          <t>Ludrio 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" t="inlineStr">
+        <is>
+          <t>BEGASA</t>
+        </is>
+      </c>
+      <c r="B2697" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="C2697" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="D2697" t="inlineStr">
+        <is>
+          <t>SETE PONTES</t>
+        </is>
+      </c>
+      <c r="E2697" t="n">
+        <v>43.313950644662</v>
+      </c>
+      <c r="F2697" t="n">
+        <v>-7.663689559420194</v>
+      </c>
+      <c r="G2697" t="inlineStr">
+        <is>
+          <t>P.G.R. 400 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2698">
+      <c r="A2698" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2698" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2698" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2698" t="inlineStr">
+        <is>
+          <t>AMETLLA 20kV</t>
+        </is>
+      </c>
+      <c r="E2698" t="n">
+        <v>41.67085469247153</v>
+      </c>
+      <c r="F2698" t="n">
+        <v>2.271649227505146</v>
+      </c>
+      <c r="G2698" t="inlineStr">
+        <is>
+          <t>FRANQUESES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2699" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2699" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2699" t="inlineStr">
+        <is>
+          <t>AMETLLA 40kV</t>
+        </is>
+      </c>
+      <c r="E2699" t="n">
+        <v>41.67085469247153</v>
+      </c>
+      <c r="F2699" t="n">
+        <v>2.271649227505146</v>
+      </c>
+      <c r="G2699" t="inlineStr">
+        <is>
+          <t>FRANQUESES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2700" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2700" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2700" t="inlineStr">
+        <is>
+          <t>CENTELLES 40kV</t>
+        </is>
+      </c>
+      <c r="E2700" t="n">
+        <v>41.80745276095795</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>2.212826027379293</v>
+      </c>
+      <c r="G2700" t="inlineStr">
+        <is>
+          <t>CENTELLES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2701" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2701" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2701" t="inlineStr">
+        <is>
+          <t>GAFA 40kV</t>
+        </is>
+      </c>
+      <c r="E2701" t="n">
+        <v>41.65133343670028</v>
+      </c>
+      <c r="F2701" t="n">
+        <v>2.246491305319538</v>
+      </c>
+      <c r="G2701" t="inlineStr">
+        <is>
+          <t>FRANQUESES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2702" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2702" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2702" t="inlineStr">
+        <is>
+          <t>MARGENS 20kV</t>
+        </is>
+      </c>
+      <c r="E2702" t="n">
+        <v>41.64261625048951</v>
+      </c>
+      <c r="F2702" t="n">
+        <v>2.282441482979596</v>
+      </c>
+      <c r="G2702" t="inlineStr">
+        <is>
+          <t>FRANQUESES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2703">
+      <c r="A2703" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2703" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2703" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2703" t="inlineStr">
+        <is>
+          <t>MARGENS 40kV</t>
+        </is>
+      </c>
+      <c r="E2703" t="n">
+        <v>41.64261625048951</v>
+      </c>
+      <c r="F2703" t="n">
+        <v>2.282441482979596</v>
+      </c>
+      <c r="G2703" t="inlineStr">
+        <is>
+          <t>FRANQUESES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2704" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2704" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2704" t="inlineStr">
+        <is>
+          <t>MOTOR 40kV</t>
+        </is>
+      </c>
+      <c r="E2704" t="n">
+        <v>41.80134298350656</v>
+      </c>
+      <c r="F2704" t="n">
+        <v>2.226194127987237</v>
+      </c>
+      <c r="G2704" t="inlineStr">
+        <is>
+          <t>CENTELLES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2705" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2705" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2705" t="inlineStr">
+        <is>
+          <t>REC 20kV</t>
+        </is>
+      </c>
+      <c r="E2705" t="n">
+        <v>41.60992236180914</v>
+      </c>
+      <c r="F2705" t="n">
+        <v>2.285200026592213</v>
+      </c>
+      <c r="G2705" t="inlineStr">
+        <is>
+          <t>FRANQUESES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2706" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2706" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2706" t="inlineStr">
+        <is>
+          <t>REC 5kV</t>
+        </is>
+      </c>
+      <c r="E2706" t="n">
+        <v>41.60992236180914</v>
+      </c>
+      <c r="F2706" t="n">
+        <v>2.285200026592213</v>
+      </c>
+      <c r="G2706" t="inlineStr">
+        <is>
+          <t>FRANQUESES 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2707" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2707" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2707" t="inlineStr">
+        <is>
+          <t>SANT PERE 20kV</t>
+        </is>
+      </c>
+      <c r="E2707" t="n">
+        <v>42.07489126934011</v>
+      </c>
+      <c r="F2707" t="n">
+        <v>2.301011099286454</v>
+      </c>
+      <c r="G2707" t="inlineStr">
+        <is>
+          <t>VIC 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2708" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2708" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2708" t="inlineStr">
+        <is>
+          <t>SANT PERE 40kV</t>
+        </is>
+      </c>
+      <c r="E2708" t="n">
+        <v>42.07489126934011</v>
+      </c>
+      <c r="F2708" t="n">
+        <v>2.301011099286454</v>
+      </c>
+      <c r="G2708" t="inlineStr">
+        <is>
+          <t>VIC 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2709" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2709" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2709" t="inlineStr">
+        <is>
+          <t>SANT PERE 5kV</t>
+        </is>
+      </c>
+      <c r="E2709" t="n">
+        <v>42.07489126934011</v>
+      </c>
+      <c r="F2709" t="n">
+        <v>2.301011099286454</v>
+      </c>
+      <c r="G2709" t="inlineStr">
+        <is>
+          <t>VIC 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2710" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2710" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D2710" t="inlineStr">
+        <is>
+          <t>VIC 40kV</t>
+        </is>
+      </c>
+      <c r="E2710" t="n">
+        <v>41.9558690108909</v>
+      </c>
+      <c r="F2710" t="n">
+        <v>2.282203299405405</v>
+      </c>
+      <c r="G2710" t="inlineStr">
+        <is>
+          <t>VIC 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2711">
+      <c r="A2711" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2711" t="inlineStr">
+        <is>
+          <t>Provincia no encontrada</t>
+        </is>
+      </c>
+      <c r="C2711" t="inlineStr"/>
+      <c r="D2711" t="inlineStr">
+        <is>
+          <t>Información complementaria sobre sobre los nudos:</t>
+        </is>
+      </c>
+      <c r="E2711" t="inlineStr"/>
+      <c r="F2711" t="inlineStr"/>
+      <c r="G2711" t="inlineStr"/>
+    </row>
+    <row r="2712">
+      <c r="A2712" t="inlineStr">
+        <is>
+          <t>ANELL</t>
+        </is>
+      </c>
+      <c r="B2712" t="inlineStr">
+        <is>
+          <t>Provincia no encontrada</t>
+        </is>
+      </c>
+      <c r="C2712" t="inlineStr"/>
+      <c r="D2712" t="inlineStr">
+        <is>
+          <t>(1) Nudo a desaparecer
+(2) Previsto cambio de tensión de 5kV a 20kV
+(3) Nudo de afección mayoritaria a la red de transporte
+(4) Valor sujeto a análisis del conjunto de red o con otros gestores de la red de distribución
+(5) Subestación con espacio insuficiente o posibles restricciones para su ampliación. Dificultad para la conexión de una nueva posición o con coste muy elevado
+(6) Capacidad que podría no estar disponible en función de la explotación de sus barras. A determinar en estudio individual.</t>
+        </is>
+      </c>
+      <c r="E2712" t="inlineStr"/>
+      <c r="F2712" t="inlineStr"/>
+      <c r="G2712" t="inlineStr"/>
+    </row>
+    <row r="2713">
+      <c r="A2713" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2713" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2713" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2713" t="n">
+        <v>1463897</v>
+      </c>
+      <c r="E2713" t="n">
+        <v>36.53637322527722</v>
+      </c>
+      <c r="F2713" t="n">
+        <v>-6.294249248417045</v>
+      </c>
+      <c r="G2713" t="inlineStr"/>
+    </row>
+    <row r="2714">
+      <c r="A2714" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2714" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2714" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2714" t="n">
+        <v>1463839</v>
+      </c>
+      <c r="E2714" t="n">
+        <v>36.50465985568528</v>
+      </c>
+      <c r="F2714" t="n">
+        <v>-6.265022628195864</v>
+      </c>
+      <c r="G2714" t="inlineStr"/>
+    </row>
+    <row r="2715">
+      <c r="A2715" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2715" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2715" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2715" t="n">
+        <v>1463769</v>
+      </c>
+      <c r="E2715" t="n">
+        <v>36.52127933431678</v>
+      </c>
+      <c r="F2715" t="n">
+        <v>-6.286157166243863</v>
+      </c>
+      <c r="G2715" t="inlineStr"/>
+    </row>
+    <row r="2716">
+      <c r="A2716" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2716" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2716" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2716" t="n">
+        <v>1463783</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>36.4903822411298</v>
+      </c>
+      <c r="F2716" t="n">
+        <v>-6.266550889549928</v>
+      </c>
+      <c r="G2716" t="inlineStr"/>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2717" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2717" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2717" t="n">
+        <v>1463825</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>36.49066814368274</v>
+      </c>
+      <c r="F2717" t="n">
+        <v>-6.266367558726361</v>
+      </c>
+      <c r="G2717" t="inlineStr"/>
+    </row>
+    <row r="2718">
+      <c r="A2718" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2718" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2718" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2718" t="n">
+        <v>2291763</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>36.5227441467191</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>-6.279419777655289</v>
+      </c>
+      <c r="G2718" t="inlineStr"/>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2719" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2719" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2719" t="n">
+        <v>1463811</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>36.4986251673341</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>-6.270707738665145</v>
+      </c>
+      <c r="G2719" t="inlineStr"/>
+    </row>
+    <row r="2720">
+      <c r="A2720" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2720" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2720" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2720" t="n">
+        <v>1554117</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>36.51810667516945</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>-6.278484904934086</v>
+      </c>
+      <c r="G2720" t="inlineStr"/>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2721" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2721" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2721" t="n">
+        <v>1463910</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>36.5064097020845</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>-6.264792140574106</v>
+      </c>
+      <c r="G2721" t="inlineStr"/>
+    </row>
+    <row r="2722">
+      <c r="A2722" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2722" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2722" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2722" t="n">
+        <v>1108231</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>36.53283864767032</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>-6.303795881211367</v>
+      </c>
+      <c r="G2722" t="inlineStr"/>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2723" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2723" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2723" t="n">
+        <v>1463923</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>36.51040802485864</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>-6.277671149670601</v>
+      </c>
+      <c r="G2723" t="inlineStr"/>
+    </row>
+    <row r="2724">
+      <c r="A2724" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2724" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2724" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2724" t="n">
+        <v>1463937</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>36.51261442391162</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>-6.274627479504671</v>
+      </c>
+      <c r="G2724" t="inlineStr"/>
+    </row>
+    <row r="2725">
+      <c r="A2725" t="inlineStr">
+        <is>
+          <t>SEDC</t>
+        </is>
+      </c>
+      <c r="B2725" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2725" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2725" t="n">
+        <v>1472567</v>
+      </c>
+      <c r="E2725" t="n">
+        <v>36.53067001060644</v>
+      </c>
+      <c r="F2725" t="n">
+        <v>-6.288294462203017</v>
+      </c>
+      <c r="G2725" t="inlineStr"/>
+    </row>
+    <row r="2726">
+      <c r="A2726" t="inlineStr">
+        <is>
+          <t>EASA</t>
+        </is>
+      </c>
+      <c r="B2726" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="C2726" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="D2726" t="inlineStr">
+        <is>
+          <t>BAÑOS</t>
+        </is>
+      </c>
+      <c r="E2726" t="n">
+        <v>42.76212635703909</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>-0.2324169166506727</v>
+      </c>
+      <c r="G2726" t="inlineStr">
+        <is>
+          <t>SABIÑANIGO 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" t="inlineStr">
+        <is>
+          <t>EASA</t>
+        </is>
+      </c>
+      <c r="B2727" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="C2727" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="D2727" t="inlineStr">
+        <is>
+          <t>ERISTE</t>
+        </is>
+      </c>
+      <c r="E2727" t="n">
+        <v>42.5889306999028</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.4920707922577778</v>
+      </c>
+      <c r="G2727" t="inlineStr">
+        <is>
+          <t>ERISTE 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" t="inlineStr">
+        <is>
+          <t>EASA</t>
+        </is>
+      </c>
+      <c r="B2728" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="C2728" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="D2728" t="inlineStr">
+        <is>
+          <t>PUEYO</t>
+        </is>
+      </c>
+      <c r="E2728" t="n">
+        <v>42.72872016289656</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>-0.3056477985208639</v>
+      </c>
+      <c r="G2728" t="inlineStr">
+        <is>
+          <t>SABIÑANIGO 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" t="inlineStr">
+        <is>
+          <t>EASA</t>
+        </is>
+      </c>
+      <c r="B2729" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="C2729" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="D2729" t="inlineStr">
+        <is>
+          <t>SABIÑANIGO</t>
+        </is>
+      </c>
+      <c r="E2729" t="n">
+        <v>42.51681745522851</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>-0.358014483313274</v>
+      </c>
+      <c r="G2729" t="inlineStr">
+        <is>
+          <t>SABIÑANIGO 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" t="inlineStr">
+        <is>
+          <t>EASA</t>
+        </is>
+      </c>
+      <c r="B2730" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="C2730" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="D2730" t="inlineStr">
+        <is>
+          <t>SALLENT</t>
+        </is>
+      </c>
+      <c r="E2730" t="n">
+        <v>42.77060218033812</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>-0.3337306311219858</v>
+      </c>
+      <c r="G2730" t="inlineStr">
+        <is>
+          <t>SABIÑANIGO 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" t="inlineStr">
+        <is>
+          <t>PITARCH</t>
+        </is>
+      </c>
+      <c r="B2731" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="C2731" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D2731" t="inlineStr">
+        <is>
+          <t>EPST05</t>
+        </is>
+      </c>
+      <c r="E2731" t="n">
+        <v>39.95820488090158</v>
+      </c>
+      <c r="F2731" t="n">
+        <v>-6.51297738168588</v>
+      </c>
+      <c r="G2731" t="inlineStr">
+        <is>
+          <t>Cáceres 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" t="inlineStr">
+        <is>
+          <t>PITARCH</t>
+        </is>
+      </c>
+      <c r="B2732" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="C2732" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D2732" t="inlineStr">
+        <is>
+          <t>EPST04</t>
+        </is>
+      </c>
+      <c r="E2732" t="n">
+        <v>39.66775400571577</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>-6.485004321355703</v>
+      </c>
+      <c r="G2732" t="inlineStr">
+        <is>
+          <t>Cáceres 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" t="inlineStr">
+        <is>
+          <t>PITARCH</t>
+        </is>
+      </c>
+      <c r="B2733" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="C2733" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D2733" t="inlineStr">
+        <is>
+          <t>EPST01</t>
+        </is>
+      </c>
+      <c r="E2733" t="n">
+        <v>39.50650750728765</v>
+      </c>
+      <c r="F2733" t="n">
+        <v>-6.366131371464301</v>
+      </c>
+      <c r="G2733" t="inlineStr">
+        <is>
+          <t>Cáceres 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" t="inlineStr">
+        <is>
+          <t>PITARCH</t>
+        </is>
+      </c>
+      <c r="B2734" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="C2734" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D2734" t="inlineStr">
+        <is>
+          <t>EPST06</t>
+        </is>
+      </c>
+      <c r="E2734" t="n">
+        <v>39.81585364001706</v>
+      </c>
+      <c r="F2734" t="n">
+        <v>-6.478470293989872</v>
+      </c>
+      <c r="G2734" t="inlineStr">
+        <is>
+          <t>Cáceres 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" t="inlineStr">
+        <is>
+          <t>PITARCH</t>
+        </is>
+      </c>
+      <c r="B2735" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="C2735" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D2735" t="inlineStr">
+        <is>
+          <t>EPST02</t>
+        </is>
+      </c>
+      <c r="E2735" t="n">
+        <v>39.4433053518851</v>
+      </c>
+      <c r="F2735" t="n">
+        <v>-6.256982652951003</v>
+      </c>
+      <c r="G2735" t="inlineStr">
+        <is>
+          <t>Cáceres 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" t="inlineStr">
+        <is>
+          <t>PITARCH</t>
+        </is>
+      </c>
+      <c r="B2736" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="C2736" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D2736" t="inlineStr">
+        <is>
+          <t>EPST03</t>
+        </is>
+      </c>
+      <c r="E2736" t="n">
+        <v>39.35099133397201</v>
+      </c>
+      <c r="F2736" t="n">
+        <v>-6.185162945467881</v>
+      </c>
+      <c r="G2736" t="inlineStr">
+        <is>
+          <t>Cáceres 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" t="inlineStr">
+        <is>
+          <t>PITARCH</t>
+        </is>
+      </c>
+      <c r="B2737" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="C2737" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D2737" t="inlineStr">
+        <is>
+          <t>EPST08</t>
+        </is>
+      </c>
+      <c r="E2737" t="n">
+        <v>39.72237633972138</v>
+      </c>
+      <c r="F2737" t="n">
+        <v>-6.877358880161323</v>
+      </c>
+      <c r="G2737" t="inlineStr"/>
+    </row>
+    <row r="2738">
+      <c r="A2738" t="inlineStr">
+        <is>
+          <t>PEUSA</t>
+        </is>
+      </c>
+      <c r="B2738" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2738" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="D2738" t="inlineStr">
+        <is>
+          <t>SE Adrall</t>
+        </is>
+      </c>
+      <c r="E2738" t="n">
+        <v>42.32375162770153</v>
+      </c>
+      <c r="F2738" t="n">
+        <v>1.39576960612606</v>
+      </c>
+      <c r="G2738" t="inlineStr">
+        <is>
+          <t>ADRALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" t="inlineStr">
+        <is>
+          <t>CONQUENSE</t>
+        </is>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C2739" t="inlineStr">
+        <is>
+          <t>CUENCA</t>
+        </is>
+      </c>
+      <c r="D2739" t="inlineStr">
+        <is>
+          <t>ST EL TERMINILLO</t>
+        </is>
+      </c>
+      <c r="E2739" t="n">
+        <v>40.05935609997702</v>
+      </c>
+      <c r="F2739" t="n">
+        <v>-2.162725749809557</v>
+      </c>
+      <c r="G2739" t="inlineStr">
+        <is>
+          <t>BOLARQUE 132 / OLMEDILLA 132</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Distribucion/Excels/subestaciones_distribucion.xlsx
+++ b/Distribucion/Excels/subestaciones_distribucion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2739"/>
+  <dimension ref="A1:G2752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90659,7 +90659,7 @@
     <row r="2738">
       <c r="A2738" t="inlineStr">
         <is>
-          <t>PEUSA</t>
+          <t>BASSOLS</t>
         </is>
       </c>
       <c r="B2738" t="inlineStr">
@@ -90669,54 +90669,449 @@
       </c>
       <c r="C2738" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="D2738" t="inlineStr">
         <is>
-          <t>SE Adrall</t>
+          <t>SEOLO</t>
         </is>
       </c>
       <c r="E2738" t="n">
-        <v>42.32375162770153</v>
+        <v>42.1902339101795</v>
       </c>
       <c r="F2738" t="n">
-        <v>1.39576960612606</v>
+        <v>-3.509188476524294</v>
       </c>
       <c r="G2738" t="inlineStr">
         <is>
-          <t>ADRALL</t>
+          <t>BESCANO 400</t>
         </is>
       </c>
     </row>
     <row r="2739">
       <c r="A2739" t="inlineStr">
         <is>
+          <t>BASSOLS</t>
+        </is>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2739" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D2739" t="inlineStr">
+        <is>
+          <t>SESER</t>
+        </is>
+      </c>
+      <c r="E2739" t="n">
+        <v>42.18059763860033</v>
+      </c>
+      <c r="F2739" t="n">
+        <v>-3.261968966507627</v>
+      </c>
+      <c r="G2739" t="inlineStr">
+        <is>
+          <t>SANTA LLOGAIA 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" t="inlineStr">
+        <is>
+          <t>BASSOLS</t>
+        </is>
+      </c>
+      <c r="B2740" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2740" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D2740" t="inlineStr">
+        <is>
+          <t>SEPOL</t>
+        </is>
+      </c>
+      <c r="E2740" t="n">
+        <v>42.21956551278521</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>-3.411616626690947</v>
+      </c>
+      <c r="G2740" t="inlineStr">
+        <is>
+          <t>VIC 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" t="inlineStr">
+        <is>
+          <t>MAESTRAZGO</t>
+        </is>
+      </c>
+      <c r="B2741" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="C2741" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="D2741" t="n">
+        <v>90012</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>40.55853380970881</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>0.3686606015468774</v>
+      </c>
+      <c r="G2741" t="inlineStr"/>
+    </row>
+    <row r="2742">
+      <c r="A2742" t="inlineStr">
+        <is>
+          <t>MAESTRAZGO</t>
+        </is>
+      </c>
+      <c r="B2742" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="C2742" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="D2742" t="n">
+        <v>38050</v>
+      </c>
+      <c r="E2742" t="n">
+        <v>40.62142737264323</v>
+      </c>
+      <c r="F2742" t="n">
+        <v>-0.09814474033046774</v>
+      </c>
+      <c r="G2742" t="inlineStr"/>
+    </row>
+    <row r="2743">
+      <c r="A2743" t="inlineStr">
+        <is>
+          <t>MAESTRAZGO</t>
+        </is>
+      </c>
+      <c r="B2743" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="C2743" t="inlineStr">
+        <is>
+          <t>Teruel</t>
+        </is>
+      </c>
+      <c r="D2743" t="n">
+        <v>90004</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>40.83769974173948</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>-0.2464551951109927</v>
+      </c>
+      <c r="G2743" t="inlineStr"/>
+    </row>
+    <row r="2744">
+      <c r="A2744" t="inlineStr">
+        <is>
+          <t>MAESTRAZGO</t>
+        </is>
+      </c>
+      <c r="B2744" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="C2744" t="inlineStr">
+        <is>
+          <t>Teruel</t>
+        </is>
+      </c>
+      <c r="D2744" t="n">
+        <v>13002</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>40.79921202891665</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>-0.3151422778399606</v>
+      </c>
+      <c r="G2744" t="inlineStr"/>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="inlineStr">
+        <is>
+          <t>MAESTRAZGO</t>
+        </is>
+      </c>
+      <c r="B2745" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="C2745" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="D2745" t="n">
+        <v>38046</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>40.66991731226165</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>-0.06025320802908805</v>
+      </c>
+      <c r="G2745" t="inlineStr"/>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="inlineStr">
+        <is>
+          <t>GARVEY</t>
+        </is>
+      </c>
+      <c r="B2746" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2746" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="D2746" t="inlineStr">
+        <is>
+          <t>SE SANTA AMELIA</t>
+        </is>
+      </c>
+      <c r="E2746" t="n">
+        <v>37.29431064143461</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>-6.308439361481372</v>
+      </c>
+      <c r="G2746" t="inlineStr">
+        <is>
+          <t>ROCIO 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="inlineStr">
+        <is>
+          <t>GARVEY</t>
+        </is>
+      </c>
+      <c r="B2747" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2747" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="D2747" t="inlineStr">
+        <is>
+          <t>SE BENACAZON</t>
+        </is>
+      </c>
+      <c r="E2747" t="n">
+        <v>37.36756591196588</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>-6.243222104267288</v>
+      </c>
+      <c r="G2747" t="inlineStr">
+        <is>
+          <t>CHUCENA 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="inlineStr">
+        <is>
+          <t>GARVEY</t>
+        </is>
+      </c>
+      <c r="B2748" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2748" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="D2748" t="inlineStr">
+        <is>
+          <t>SUBESTACION CHUCENA-MGE</t>
+        </is>
+      </c>
+      <c r="E2748" t="n">
+        <v>37.34173429969156</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>-6.38347392603499</v>
+      </c>
+      <c r="G2748" t="inlineStr">
+        <is>
+          <t>CHUCENA 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="inlineStr">
+        <is>
+          <t>CUERVA</t>
+        </is>
+      </c>
+      <c r="B2749" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2749" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="D2749" t="inlineStr">
+        <is>
+          <t>036.SBT.JC308264128</t>
+        </is>
+      </c>
+      <c r="E2749" t="n">
+        <v>37.23955957210182</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>-3.88360149435025</v>
+      </c>
+      <c r="G2749" t="inlineStr">
+        <is>
+          <t>Illora 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="inlineStr">
+        <is>
+          <t>CUERVA</t>
+        </is>
+      </c>
+      <c r="B2750" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2750" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="D2750" t="inlineStr">
+        <is>
+          <t>036.SBT.AP40000001</t>
+        </is>
+      </c>
+      <c r="E2750" t="n">
+        <v>37.08790078494792</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>-3.750798486551257</v>
+      </c>
+      <c r="G2750" t="inlineStr"/>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>PEUSA</t>
+        </is>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2751" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="D2751" t="inlineStr">
+        <is>
+          <t>SE Adrall</t>
+        </is>
+      </c>
+      <c r="E2751" t="n">
+        <v>42.32375162770153</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>1.39576960612606</v>
+      </c>
+      <c r="G2751" t="inlineStr">
+        <is>
+          <t>ADRALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
           <t>CONQUENSE</t>
         </is>
       </c>
-      <c r="B2739" t="inlineStr">
+      <c r="B2752" t="inlineStr">
         <is>
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="C2739" t="inlineStr">
+      <c r="C2752" t="inlineStr">
         <is>
           <t>CUENCA</t>
         </is>
       </c>
-      <c r="D2739" t="inlineStr">
+      <c r="D2752" t="inlineStr">
         <is>
           <t>ST EL TERMINILLO</t>
         </is>
       </c>
-      <c r="E2739" t="n">
+      <c r="E2752" t="n">
         <v>40.05935609997702</v>
       </c>
-      <c r="F2739" t="n">
+      <c r="F2752" t="n">
         <v>-2.162725749809557</v>
       </c>
-      <c r="G2739" t="inlineStr">
+      <c r="G2752" t="inlineStr">
         <is>
           <t>BOLARQUE 132 / OLMEDILLA 132</t>
         </is>

--- a/Distribucion/Excels/subestaciones_distribucion.xlsx
+++ b/Distribucion/Excels/subestaciones_distribucion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2752"/>
+  <dimension ref="A1:G2756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90992,126 +90992,246 @@
     <row r="2749">
       <c r="A2749" t="inlineStr">
         <is>
-          <t>CUERVA</t>
+          <t>ADURIZ</t>
         </is>
       </c>
       <c r="B2749" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C2749" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="D2749" t="inlineStr">
         <is>
-          <t>036.SBT.JC308264128</t>
+          <t>STRM001</t>
         </is>
       </c>
       <c r="E2749" t="n">
-        <v>37.23955957210182</v>
+        <v>42.91465499797555</v>
       </c>
       <c r="F2749" t="n">
-        <v>-3.88360149435025</v>
-      </c>
-      <c r="G2749" t="inlineStr">
-        <is>
-          <t>Illora 220</t>
-        </is>
-      </c>
+        <v>-3.476347553314016</v>
+      </c>
+      <c r="G2749" t="inlineStr"/>
     </row>
     <row r="2750">
       <c r="A2750" t="inlineStr">
         <is>
-          <t>CUERVA</t>
+          <t>ADURIZ</t>
         </is>
       </c>
       <c r="B2750" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C2750" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="D2750" t="inlineStr">
         <is>
-          <t>036.SBT.AP40000001</t>
+          <t>STRM002</t>
         </is>
       </c>
       <c r="E2750" t="n">
-        <v>37.08790078494792</v>
+        <v>42.92039562214835</v>
       </c>
       <c r="F2750" t="n">
-        <v>-3.750798486551257</v>
+        <v>-3.501688918871553</v>
       </c>
       <c r="G2750" t="inlineStr"/>
     </row>
     <row r="2751">
       <c r="A2751" t="inlineStr">
         <is>
-          <t>PEUSA</t>
+          <t>ADURIZ</t>
         </is>
       </c>
       <c r="B2751" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C2751" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="D2751" t="inlineStr">
         <is>
-          <t>SE Adrall</t>
+          <t>STR003</t>
         </is>
       </c>
       <c r="E2751" t="n">
-        <v>42.32375162770153</v>
+        <v>43.06045464524659</v>
       </c>
       <c r="F2751" t="n">
-        <v>1.39576960612606</v>
-      </c>
-      <c r="G2751" t="inlineStr">
-        <is>
-          <t>ADRALL</t>
-        </is>
-      </c>
+        <v>-3.529017944416845</v>
+      </c>
+      <c r="G2751" t="inlineStr"/>
     </row>
     <row r="2752">
       <c r="A2752" t="inlineStr">
         <is>
+          <t>AGRI</t>
+        </is>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D2752" t="inlineStr">
+        <is>
+          <t>SE PLAN ESTANY</t>
+        </is>
+      </c>
+      <c r="E2752" t="n">
+        <v>42.04444260168852</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>2.821882516581669</v>
+      </c>
+      <c r="G2752" t="inlineStr">
+        <is>
+          <t>JUIA 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>CUERVA</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="D2753" t="inlineStr">
+        <is>
+          <t>036.SBT.JC308264128</t>
+        </is>
+      </c>
+      <c r="E2753" t="n">
+        <v>37.23955957210182</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>-3.88360149435025</v>
+      </c>
+      <c r="G2753" t="inlineStr">
+        <is>
+          <t>Illora 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>CUERVA</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="D2754" t="inlineStr">
+        <is>
+          <t>036.SBT.AP40000001</t>
+        </is>
+      </c>
+      <c r="E2754" t="n">
+        <v>37.08790078494792</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>-3.750798486551257</v>
+      </c>
+      <c r="G2754" t="inlineStr"/>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>PEUSA</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="D2755" t="inlineStr">
+        <is>
+          <t>SE Adrall</t>
+        </is>
+      </c>
+      <c r="E2755" t="n">
+        <v>42.32375162770153</v>
+      </c>
+      <c r="F2755" t="n">
+        <v>1.39576960612606</v>
+      </c>
+      <c r="G2755" t="inlineStr">
+        <is>
+          <t>ADRALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
           <t>CONQUENSE</t>
         </is>
       </c>
-      <c r="B2752" t="inlineStr">
+      <c r="B2756" t="inlineStr">
         <is>
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="C2752" t="inlineStr">
+      <c r="C2756" t="inlineStr">
         <is>
           <t>CUENCA</t>
         </is>
       </c>
-      <c r="D2752" t="inlineStr">
+      <c r="D2756" t="inlineStr">
         <is>
           <t>ST EL TERMINILLO</t>
         </is>
       </c>
-      <c r="E2752" t="n">
+      <c r="E2756" t="n">
         <v>40.05935609997702</v>
       </c>
-      <c r="F2752" t="n">
+      <c r="F2756" t="n">
         <v>-2.162725749809557</v>
       </c>
-      <c r="G2752" t="inlineStr">
+      <c r="G2756" t="inlineStr">
         <is>
           <t>BOLARQUE 132 / OLMEDILLA 132</t>
         </is>

--- a/Distribucion/Excels/subestaciones_distribucion.xlsx
+++ b/Distribucion/Excels/subestaciones_distribucion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2756"/>
+  <dimension ref="A1:G2772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91112,35 +91112,31 @@
     <row r="2753">
       <c r="A2753" t="inlineStr">
         <is>
-          <t>CUERVA</t>
+          <t>CALDENSE</t>
         </is>
       </c>
       <c r="B2753" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C2753" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D2753" t="inlineStr">
         <is>
-          <t>036.SBT.JC308264128</t>
+          <t>SE CAN VINYALS</t>
         </is>
       </c>
       <c r="E2753" t="n">
-        <v>37.23955957210182</v>
+        <v>41.61898616368803</v>
       </c>
       <c r="F2753" t="n">
-        <v>-3.88360149435025</v>
-      </c>
-      <c r="G2753" t="inlineStr">
-        <is>
-          <t>Illora 220</t>
-        </is>
-      </c>
+        <v>2.11536349090384</v>
+      </c>
+      <c r="G2753" t="inlineStr"/>
     </row>
     <row r="2754">
       <c r="A2754" t="inlineStr">
@@ -91160,78 +91156,558 @@
       </c>
       <c r="D2754" t="inlineStr">
         <is>
-          <t>036.SBT.AP40000001</t>
+          <t>036.SBT.JC308264128</t>
         </is>
       </c>
       <c r="E2754" t="n">
-        <v>37.08790078494792</v>
+        <v>37.23955957210182</v>
       </c>
       <c r="F2754" t="n">
-        <v>-3.750798486551257</v>
-      </c>
-      <c r="G2754" t="inlineStr"/>
+        <v>-3.88360149435025</v>
+      </c>
+      <c r="G2754" t="inlineStr">
+        <is>
+          <t>Illora 220</t>
+        </is>
+      </c>
     </row>
     <row r="2755">
       <c r="A2755" t="inlineStr">
         <is>
-          <t>PEUSA</t>
+          <t>CUERVA</t>
         </is>
       </c>
       <c r="B2755" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C2755" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="D2755" t="inlineStr">
         <is>
-          <t>SE Adrall</t>
+          <t>036.SBT.AP40000001</t>
         </is>
       </c>
       <c r="E2755" t="n">
-        <v>42.32375162770153</v>
+        <v>37.08790078494792</v>
       </c>
       <c r="F2755" t="n">
-        <v>1.39576960612606</v>
-      </c>
-      <c r="G2755" t="inlineStr">
-        <is>
-          <t>ADRALL</t>
-        </is>
-      </c>
+        <v>-3.750798486551257</v>
+      </c>
+      <c r="G2755" t="inlineStr"/>
     </row>
     <row r="2756">
       <c r="A2756" t="inlineStr">
         <is>
+          <t>GUADIELA</t>
+        </is>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="D2756" t="inlineStr">
+        <is>
+          <t>Albendea</t>
+        </is>
+      </c>
+      <c r="E2756" t="n">
+        <v>40.47857158145671</v>
+      </c>
+      <c r="F2756" t="n">
+        <v>-2.377933811299012</v>
+      </c>
+      <c r="G2756" t="inlineStr"/>
+    </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>GUADIELA</t>
+        </is>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C2757" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="D2757" t="inlineStr">
+        <is>
+          <t>Alcantud</t>
+        </is>
+      </c>
+      <c r="E2757" t="n">
+        <v>40.5327833699363</v>
+      </c>
+      <c r="F2757" t="n">
+        <v>-2.283907273213826</v>
+      </c>
+      <c r="G2757" t="inlineStr"/>
+    </row>
+    <row r="2758">
+      <c r="A2758" t="inlineStr">
+        <is>
+          <t>GUADIELA</t>
+        </is>
+      </c>
+      <c r="B2758" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C2758" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="D2758" t="inlineStr">
+        <is>
+          <t>Carrascosa de la Sierra</t>
+        </is>
+      </c>
+      <c r="E2758" t="n">
+        <v>40.55058478964145</v>
+      </c>
+      <c r="F2758" t="n">
+        <v>-2.229295455095759</v>
+      </c>
+      <c r="G2758" t="inlineStr"/>
+    </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>GUADIELA</t>
+        </is>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C2759" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="D2759" t="inlineStr">
+        <is>
+          <t>El Pozuelo</t>
+        </is>
+      </c>
+      <c r="E2759" t="n">
+        <v>40.61799967247728</v>
+      </c>
+      <c r="F2759" t="n">
+        <v>-2.272712757722092</v>
+      </c>
+      <c r="G2759" t="inlineStr"/>
+    </row>
+    <row r="2760">
+      <c r="A2760" t="inlineStr">
+        <is>
+          <t>GUADIELA</t>
+        </is>
+      </c>
+      <c r="B2760" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C2760" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="D2760" t="inlineStr">
+        <is>
+          <t>Cañizares</t>
+        </is>
+      </c>
+      <c r="E2760" t="n">
+        <v>40.5301349830192</v>
+      </c>
+      <c r="F2760" t="n">
+        <v>-2.149704313407788</v>
+      </c>
+      <c r="G2760" t="inlineStr"/>
+    </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>GUADIELA</t>
+        </is>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C2761" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="D2761" t="inlineStr">
+        <is>
+          <t>Cañizares2</t>
+        </is>
+      </c>
+      <c r="E2761" t="n">
+        <v>40.55197384173102</v>
+      </c>
+      <c r="F2761" t="n">
+        <v>-2.17855300635147</v>
+      </c>
+      <c r="G2761" t="inlineStr"/>
+    </row>
+    <row r="2762">
+      <c r="A2762" t="inlineStr">
+        <is>
+          <t>GUADIELA</t>
+        </is>
+      </c>
+      <c r="B2762" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="C2762" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="D2762" t="inlineStr">
+        <is>
+          <t>Beteta</t>
+        </is>
+      </c>
+      <c r="E2762" t="n">
+        <v>40.57227507458095</v>
+      </c>
+      <c r="F2762" t="n">
+        <v>-2.078817970410711</v>
+      </c>
+      <c r="G2762" t="inlineStr"/>
+    </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>CREVILLENT</t>
+        </is>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="C2763" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="D2763" t="inlineStr">
+        <is>
+          <t>ST Crevillent</t>
+        </is>
+      </c>
+      <c r="E2763" t="n">
+        <v>38.2312491392356</v>
+      </c>
+      <c r="F2763" t="n">
+        <v>-0.7848999280341946</v>
+      </c>
+      <c r="G2763" t="inlineStr"/>
+    </row>
+    <row r="2764">
+      <c r="A2764" t="inlineStr">
+        <is>
+          <t>PROHIDA</t>
+        </is>
+      </c>
+      <c r="B2764" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+      <c r="C2764" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="D2764" t="inlineStr">
+        <is>
+          <t>SUBSPM2T0500370P</t>
+        </is>
+      </c>
+      <c r="E2764" t="n">
+        <v>42.93691243943881</v>
+      </c>
+      <c r="F2764" t="n">
+        <v>-6.318151563201072</v>
+      </c>
+      <c r="G2764" t="inlineStr">
+        <is>
+          <t>VILLABLINO 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>PROHIDA</t>
+        </is>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+      <c r="C2765" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="D2765" t="inlineStr">
+        <is>
+          <t>SUBSPM3T1000530P</t>
+        </is>
+      </c>
+      <c r="E2765" t="n">
+        <v>42.94017379805134</v>
+      </c>
+      <c r="F2765" t="n">
+        <v>-6.285397227802542</v>
+      </c>
+      <c r="G2765" t="inlineStr">
+        <is>
+          <t>VILLABLINO 220</t>
+        </is>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>LERSA</t>
+        </is>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D2766" t="inlineStr">
+        <is>
+          <t>SE-132</t>
+        </is>
+      </c>
+      <c r="E2766" t="n">
+        <v>57.57395650967786</v>
+      </c>
+      <c r="F2766" t="n">
+        <v>-4.097749813108122</v>
+      </c>
+      <c r="G2766" t="inlineStr"/>
+    </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>LERSA</t>
+        </is>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2767" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D2767" t="inlineStr">
+        <is>
+          <t>SE-003</t>
+        </is>
+      </c>
+      <c r="E2767" t="n">
+        <v>42.2035336823358</v>
+      </c>
+      <c r="F2767" t="n">
+        <v>-3.808151311719086</v>
+      </c>
+      <c r="G2767" t="inlineStr"/>
+    </row>
+    <row r="2768">
+      <c r="A2768" t="inlineStr">
+        <is>
+          <t>LERSA</t>
+        </is>
+      </c>
+      <c r="B2768" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2768" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D2768" t="inlineStr">
+        <is>
+          <t>SE-032</t>
+        </is>
+      </c>
+      <c r="E2768" t="n">
+        <v>42.219917922313</v>
+      </c>
+      <c r="F2768" t="n">
+        <v>-3.829839421957622</v>
+      </c>
+      <c r="G2768" t="inlineStr"/>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="inlineStr">
+        <is>
+          <t>EPR</t>
+        </is>
+      </c>
+      <c r="B2769" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="C2769" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="D2769" t="inlineStr">
+        <is>
+          <t>SUB-23001</t>
+        </is>
+      </c>
+      <c r="E2769" t="n">
+        <v>36.51950237940726</v>
+      </c>
+      <c r="F2769" t="n">
+        <v>-6.156472503195129</v>
+      </c>
+      <c r="G2769" t="inlineStr"/>
+    </row>
+    <row r="2770">
+      <c r="A2770" t="inlineStr">
+        <is>
+          <t>SOLLER</t>
+        </is>
+      </c>
+      <c r="B2770" t="inlineStr">
+        <is>
+          <t>Provincia no encontrada</t>
+        </is>
+      </c>
+      <c r="C2770" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="D2770" t="inlineStr">
+        <is>
+          <t>SE-000</t>
+        </is>
+      </c>
+      <c r="E2770" t="n">
+        <v>39.77056670534942</v>
+      </c>
+      <c r="F2770" t="n">
+        <v>2.71114279037752</v>
+      </c>
+      <c r="G2770" t="inlineStr">
+        <is>
+          <t>SOLLER 66</t>
+        </is>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="inlineStr">
+        <is>
+          <t>PEUSA</t>
+        </is>
+      </c>
+      <c r="B2771" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2771" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="D2771" t="inlineStr">
+        <is>
+          <t>SE Adrall</t>
+        </is>
+      </c>
+      <c r="E2771" t="n">
+        <v>42.32375162770153</v>
+      </c>
+      <c r="F2771" t="n">
+        <v>1.39576960612606</v>
+      </c>
+      <c r="G2771" t="inlineStr">
+        <is>
+          <t>ADRALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" t="inlineStr">
+        <is>
           <t>CONQUENSE</t>
         </is>
       </c>
-      <c r="B2756" t="inlineStr">
+      <c r="B2772" t="inlineStr">
         <is>
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="C2756" t="inlineStr">
+      <c r="C2772" t="inlineStr">
         <is>
           <t>CUENCA</t>
         </is>
       </c>
-      <c r="D2756" t="inlineStr">
+      <c r="D2772" t="inlineStr">
         <is>
           <t>ST EL TERMINILLO</t>
         </is>
       </c>
-      <c r="E2756" t="n">
+      <c r="E2772" t="n">
         <v>40.05935609997702</v>
       </c>
-      <c r="F2756" t="n">
+      <c r="F2772" t="n">
         <v>-2.162725749809557</v>
       </c>
-      <c r="G2756" t="inlineStr">
+      <c r="G2772" t="inlineStr">
         <is>
           <t>BOLARQUE 132 / OLMEDILLA 132</t>
         </is>

--- a/Distribucion/Excels/subestaciones_distribucion.xlsx
+++ b/Distribucion/Excels/subestaciones_distribucion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2772"/>
+  <dimension ref="A1:G2774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91650,64 +91650,130 @@
     <row r="2771">
       <c r="A2771" t="inlineStr">
         <is>
-          <t>PEUSA</t>
+          <t>CARBAYIN</t>
         </is>
       </c>
       <c r="B2771" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Principado de Asturias</t>
         </is>
       </c>
       <c r="C2771" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>ASTURIAS</t>
         </is>
       </c>
       <c r="D2771" t="inlineStr">
         <is>
-          <t>SE Adrall</t>
+          <t>SETLACABAÑONA</t>
         </is>
       </c>
       <c r="E2771" t="n">
-        <v>42.32375162770153</v>
+        <v>43.34764886782635</v>
       </c>
       <c r="F2771" t="n">
-        <v>1.39576960612606</v>
+        <v>-5.625634017777805</v>
       </c>
       <c r="G2771" t="inlineStr">
         <is>
-          <t>ADRALL</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="2772">
       <c r="A2772" t="inlineStr">
         <is>
+          <t>SERVILIANO</t>
+        </is>
+      </c>
+      <c r="B2772" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+      <c r="C2772" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="D2772" t="inlineStr">
+        <is>
+          <t>SUBEST_GOMEZSERRACIN</t>
+        </is>
+      </c>
+      <c r="E2772" t="n">
+        <v>41.28523969571562</v>
+      </c>
+      <c r="F2772" t="n">
+        <v>-4.322073844334967</v>
+      </c>
+      <c r="G2772" t="inlineStr">
+        <is>
+          <t>LASTRAS 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>PEUSA</t>
+        </is>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2773" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="D2773" t="inlineStr">
+        <is>
+          <t>SE Adrall</t>
+        </is>
+      </c>
+      <c r="E2773" t="n">
+        <v>42.32375162770153</v>
+      </c>
+      <c r="F2773" t="n">
+        <v>1.39576960612606</v>
+      </c>
+      <c r="G2773" t="inlineStr">
+        <is>
+          <t>ADRALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="inlineStr">
+        <is>
           <t>CONQUENSE</t>
         </is>
       </c>
-      <c r="B2772" t="inlineStr">
+      <c r="B2774" t="inlineStr">
         <is>
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="C2772" t="inlineStr">
+      <c r="C2774" t="inlineStr">
         <is>
           <t>CUENCA</t>
         </is>
       </c>
-      <c r="D2772" t="inlineStr">
+      <c r="D2774" t="inlineStr">
         <is>
           <t>ST EL TERMINILLO</t>
         </is>
       </c>
-      <c r="E2772" t="n">
+      <c r="E2774" t="n">
         <v>40.05935609997702</v>
       </c>
-      <c r="F2772" t="n">
+      <c r="F2774" t="n">
         <v>-2.162725749809557</v>
       </c>
-      <c r="G2772" t="inlineStr">
+      <c r="G2774" t="inlineStr">
         <is>
           <t>BOLARQUE 132 / OLMEDILLA 132</t>
         </is>

--- a/Distribucion/Excels/subestaciones_distribucion.xlsx
+++ b/Distribucion/Excels/subestaciones_distribucion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2774"/>
+  <dimension ref="A1:G2776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91650,130 +91650,196 @@
     <row r="2771">
       <c r="A2771" t="inlineStr">
         <is>
-          <t>CARBAYIN</t>
+          <t>CUROS</t>
         </is>
       </c>
       <c r="B2771" t="inlineStr">
         <is>
-          <t>Principado de Asturias</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C2771" t="inlineStr">
         <is>
-          <t>ASTURIAS</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="D2771" t="inlineStr">
         <is>
-          <t>SETLACABAÑONA</t>
+          <t>SEMIE</t>
         </is>
       </c>
       <c r="E2771" t="n">
-        <v>43.34764886782635</v>
+        <v>42.12556741799546</v>
       </c>
       <c r="F2771" t="n">
-        <v>-5.625634017777805</v>
+        <v>-3.3594618890154</v>
       </c>
       <c r="G2771" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SANTA LLOGAIA 400</t>
         </is>
       </c>
     </row>
     <row r="2772">
       <c r="A2772" t="inlineStr">
         <is>
-          <t>SERVILIANO</t>
+          <t>CUROS</t>
         </is>
       </c>
       <c r="B2772" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C2772" t="inlineStr">
         <is>
-          <t>Segovia</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="D2772" t="inlineStr">
         <is>
-          <t>SUBEST_GOMEZSERRACIN</t>
+          <t>SEPAU</t>
         </is>
       </c>
       <c r="E2772" t="n">
-        <v>41.28523969571562</v>
+        <v>42.14557484068172</v>
       </c>
       <c r="F2772" t="n">
-        <v>-4.322073844334967</v>
+        <v>-3.429030257934638</v>
       </c>
       <c r="G2772" t="inlineStr">
         <is>
-          <t>LASTRAS 400</t>
+          <t>BESCANO 400</t>
         </is>
       </c>
     </row>
     <row r="2773">
       <c r="A2773" t="inlineStr">
         <is>
-          <t>PEUSA</t>
+          <t>CARBAYIN</t>
         </is>
       </c>
       <c r="B2773" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Principado de Asturias</t>
         </is>
       </c>
       <c r="C2773" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>ASTURIAS</t>
         </is>
       </c>
       <c r="D2773" t="inlineStr">
         <is>
-          <t>SE Adrall</t>
+          <t>SETLACABAÑONA</t>
         </is>
       </c>
       <c r="E2773" t="n">
-        <v>42.32375162770153</v>
+        <v>43.34764886782635</v>
       </c>
       <c r="F2773" t="n">
-        <v>1.39576960612606</v>
+        <v>-5.625634017777805</v>
       </c>
       <c r="G2773" t="inlineStr">
         <is>
-          <t>ADRALL</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="2774">
       <c r="A2774" t="inlineStr">
         <is>
+          <t>SERVILIANO</t>
+        </is>
+      </c>
+      <c r="B2774" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+      <c r="C2774" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="D2774" t="inlineStr">
+        <is>
+          <t>SUBEST_GOMEZSERRACIN</t>
+        </is>
+      </c>
+      <c r="E2774" t="n">
+        <v>41.28523969571562</v>
+      </c>
+      <c r="F2774" t="n">
+        <v>-4.322073844334967</v>
+      </c>
+      <c r="G2774" t="inlineStr">
+        <is>
+          <t>LASTRAS 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>PEUSA</t>
+        </is>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="C2775" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="D2775" t="inlineStr">
+        <is>
+          <t>SE Adrall</t>
+        </is>
+      </c>
+      <c r="E2775" t="n">
+        <v>42.32375162770153</v>
+      </c>
+      <c r="F2775" t="n">
+        <v>1.39576960612606</v>
+      </c>
+      <c r="G2775" t="inlineStr">
+        <is>
+          <t>ADRALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="inlineStr">
+        <is>
           <t>CONQUENSE</t>
         </is>
       </c>
-      <c r="B2774" t="inlineStr">
+      <c r="B2776" t="inlineStr">
         <is>
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="C2774" t="inlineStr">
+      <c r="C2776" t="inlineStr">
         <is>
           <t>CUENCA</t>
         </is>
       </c>
-      <c r="D2774" t="inlineStr">
+      <c r="D2776" t="inlineStr">
         <is>
           <t>ST EL TERMINILLO</t>
         </is>
       </c>
-      <c r="E2774" t="n">
+      <c r="E2776" t="n">
         <v>40.05935609997702</v>
       </c>
-      <c r="F2774" t="n">
+      <c r="F2776" t="n">
         <v>-2.162725749809557</v>
       </c>
-      <c r="G2774" t="inlineStr">
+      <c r="G2776" t="inlineStr">
         <is>
           <t>BOLARQUE 132 / OLMEDILLA 132</t>
         </is>
